--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.033997300668483</v>
+        <v>0.1680245613586286</v>
       </c>
       <c r="D2" t="n">
-        <v>7.55154148040382</v>
+        <v>1.227125490565621</v>
       </c>
       <c r="E2" t="n">
-        <v>13.37782353196771</v>
+        <v>2.173896323944752</v>
       </c>
       <c r="F2" t="n">
-        <v>6.862501219349726</v>
+        <v>1.115156448144331</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.7896443646039</v>
+        <v>4.515817209248134</v>
       </c>
       <c r="D3" t="n">
-        <v>21.27654391910327</v>
+        <v>3.457438386854282</v>
       </c>
       <c r="E3" t="n">
-        <v>13.37782353196771</v>
+        <v>2.173896323944752</v>
       </c>
       <c r="F3" t="n">
-        <v>6.862501219349726</v>
+        <v>1.115156448144331</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
